--- a/backend/Üretim Dataları.xlsx
+++ b/backend/Üretim Dataları.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EZGİ\Desktop\hat_atama_yeni1\backend\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EZGİ\Desktop\ozgurunsonhaliilebirlesmis\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6AF926DA-218F-4E3D-8709-51DD8C66FB37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{215330BA-EDCF-4A84-99F1-5CFE11059ED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="660" yWindow="900" windowWidth="22380" windowHeight="12060" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Gelen İşçiler" sheetId="12" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10510" uniqueCount="776">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10511" uniqueCount="776">
   <si>
     <t>OP_A020060</t>
   </si>
@@ -2554,7 +2554,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -2782,6 +2782,17 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2789,7 +2800,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2958,6 +2969,9 @@
     <xf numFmtId="0" fontId="3" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -12377,7 +12391,7 @@
       <c r="E5" s="44"/>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B6" s="70" t="s">
+      <c r="B6" s="71" t="s">
         <v>767</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -12387,7 +12401,7 @@
       <c r="E6" s="44"/>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="70"/>
+      <c r="B7" s="71"/>
       <c r="C7" s="2" t="s">
         <v>660</v>
       </c>
@@ -12395,7 +12409,7 @@
       <c r="E7" s="44"/>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="70"/>
+      <c r="B8" s="71"/>
       <c r="C8" s="2" t="s">
         <v>609</v>
       </c>
@@ -33126,7 +33140,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DC0926-16DF-40D7-A7C6-DEE9A1E26DBB}">
-  <dimension ref="A1:D95"/>
+  <dimension ref="A1:D96"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="3" width="9.109375" customWidth="1"/>
@@ -34243,7 +34257,16 @@
         <v>0.8969583826794405</v>
       </c>
     </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A96" s="2" t="s">
+        <v>744</v>
+      </c>
+      <c r="B96" s="70">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/backend/Üretim Dataları.xlsx
+++ b/backend/Üretim Dataları.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EZGİ\Desktop\ozgurunsonhaliilebirlesmis\backend\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EZGİ\Desktop\denemeusttekini\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{215330BA-EDCF-4A84-99F1-5CFE11059ED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4CA17137-D9DF-438C-A43B-D3FA53CAACA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="660" yWindow="900" windowWidth="22380" windowHeight="12060" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Gelen İşçiler" sheetId="12" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10511" uniqueCount="776">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10509" uniqueCount="776">
   <si>
     <t>OP_A020060</t>
   </si>
@@ -2969,10 +2969,10 @@
     <xf numFmtId="0" fontId="3" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3258,7 +3258,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BAB532A-D2D2-4009-A1DE-594C2C255983}">
-  <dimension ref="A1:H96"/>
+  <dimension ref="A1:H94"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -3274,274 +3274,274 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="52" t="s">
-        <v>644</v>
+        <v>596</v>
       </c>
       <c r="B3" s="52"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="52" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B4" s="52"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="52" t="s">
-        <v>598</v>
+        <v>666</v>
       </c>
       <c r="B5" s="52"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="52" t="s">
-        <v>666</v>
+        <v>617</v>
       </c>
       <c r="B6" s="52"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="52" t="s">
-        <v>617</v>
+        <v>719</v>
       </c>
       <c r="B7" s="52"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="52" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B8" s="52"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="52" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B9" s="52"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="52" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B10" s="52"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="52" t="s">
-        <v>722</v>
+        <v>595</v>
       </c>
       <c r="B11" s="52"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="52" t="s">
-        <v>595</v>
+        <v>651</v>
       </c>
       <c r="B12" s="52"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="52" t="s">
-        <v>651</v>
+        <v>677</v>
       </c>
       <c r="B13" s="52"/>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="52" t="s">
-        <v>677</v>
+        <v>594</v>
       </c>
       <c r="B14" s="52"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="52" t="s">
-        <v>723</v>
+        <v>600</v>
       </c>
       <c r="B15" s="52"/>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="52" t="s">
-        <v>594</v>
+        <v>646</v>
       </c>
       <c r="B16" s="52"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="52" t="s">
-        <v>600</v>
+        <v>647</v>
       </c>
       <c r="B17" s="52"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="52" t="s">
-        <v>646</v>
+        <v>656</v>
       </c>
       <c r="B18" s="52"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="52" t="s">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="B19" s="52"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="52" t="s">
-        <v>656</v>
+        <v>611</v>
       </c>
       <c r="B20" s="52"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="52" t="s">
-        <v>635</v>
+        <v>602</v>
       </c>
       <c r="B21" s="52"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="52" t="s">
-        <v>611</v>
+        <v>716</v>
       </c>
       <c r="B22" s="52"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="52" t="s">
-        <v>602</v>
+        <v>715</v>
       </c>
       <c r="B23" s="52"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="52" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="B24" s="52"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="52" t="s">
-        <v>715</v>
+        <v>597</v>
       </c>
       <c r="B25" s="52"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="52" t="s">
-        <v>718</v>
+        <v>612</v>
       </c>
       <c r="B26" s="52"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="52" t="s">
-        <v>597</v>
+        <v>615</v>
       </c>
       <c r="B27" s="52"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="52" t="s">
-        <v>612</v>
+        <v>688</v>
       </c>
       <c r="B28" s="52"/>
       <c r="D28" s="2"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="52" t="s">
-        <v>615</v>
+        <v>689</v>
       </c>
       <c r="B29" s="52"/>
       <c r="D29" s="2"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="52" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="B30" s="52"/>
       <c r="D30" s="2"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="52" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="B31" s="52"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="52" t="s">
-        <v>694</v>
+        <v>620</v>
       </c>
       <c r="B32" s="52"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="52" t="s">
-        <v>693</v>
+        <v>625</v>
       </c>
       <c r="B33" s="52"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="52" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B34" s="52"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="52" t="s">
-        <v>625</v>
+        <v>618</v>
       </c>
       <c r="B35" s="52"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="52" t="s">
-        <v>619</v>
+        <v>630</v>
       </c>
       <c r="B36" s="52"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="52" t="s">
-        <v>618</v>
+        <v>655</v>
       </c>
       <c r="B37" s="52"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="52" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B38" s="52"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="52" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B39" s="52"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="52" t="s">
-        <v>632</v>
+        <v>724</v>
       </c>
       <c r="B40" s="52"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="52" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="B41" s="52"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="52" t="s">
-        <v>724</v>
+        <v>631</v>
       </c>
       <c r="B42" s="52"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="52" t="s">
-        <v>661</v>
+        <v>637</v>
       </c>
       <c r="B43" s="52"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="52" t="s">
-        <v>631</v>
+        <v>613</v>
       </c>
       <c r="B44" s="52"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="52" t="s">
-        <v>637</v>
+        <v>665</v>
       </c>
       <c r="B45" s="52"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="52" t="s">
-        <v>613</v>
+        <v>627</v>
       </c>
       <c r="B46" s="52"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="52" t="s">
-        <v>665</v>
+        <v>628</v>
       </c>
       <c r="B47" s="52"/>
       <c r="E47" s="19"/>
@@ -3551,284 +3551,274 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="52" t="s">
-        <v>627</v>
+        <v>702</v>
       </c>
       <c r="B48" s="52"/>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="52" t="s">
-        <v>628</v>
+        <v>703</v>
       </c>
       <c r="B49" s="52"/>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="52" t="s">
-        <v>702</v>
+        <v>707</v>
       </c>
       <c r="B50" s="52"/>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="52" t="s">
-        <v>703</v>
+        <v>607</v>
       </c>
       <c r="B51" s="52"/>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="52" t="s">
-        <v>707</v>
+        <v>608</v>
       </c>
       <c r="B52" s="52"/>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="52" t="s">
-        <v>607</v>
+        <v>654</v>
       </c>
       <c r="B53" s="52"/>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="52" t="s">
-        <v>608</v>
+        <v>658</v>
       </c>
       <c r="B54" s="52"/>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="52" t="s">
-        <v>654</v>
+        <v>725</v>
       </c>
       <c r="B55" s="52"/>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="52" t="s">
-        <v>658</v>
+        <v>726</v>
       </c>
       <c r="B56" s="52"/>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="52" t="s">
-        <v>725</v>
+        <v>695</v>
       </c>
       <c r="B57" s="52"/>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="52" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B58" s="52"/>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="52" t="s">
-        <v>695</v>
+        <v>610</v>
       </c>
       <c r="B59" s="52"/>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="52" t="s">
-        <v>727</v>
+        <v>609</v>
       </c>
       <c r="B60" s="52"/>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="52" t="s">
-        <v>610</v>
+        <v>653</v>
       </c>
       <c r="B61" s="52"/>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="52" t="s">
-        <v>609</v>
+        <v>728</v>
       </c>
       <c r="B62" s="52"/>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="52" t="s">
-        <v>653</v>
+        <v>623</v>
       </c>
       <c r="B63" s="52"/>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="52" t="s">
-        <v>728</v>
+        <v>622</v>
       </c>
       <c r="B64" s="52"/>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="52" t="s">
-        <v>623</v>
+        <v>662</v>
       </c>
       <c r="B65" s="52"/>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="52" t="s">
-        <v>622</v>
+        <v>601</v>
       </c>
       <c r="B66" s="52"/>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="52" t="s">
-        <v>662</v>
+        <v>624</v>
       </c>
       <c r="B67" s="52"/>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="52" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B68" s="52"/>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="52" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="B69" s="52"/>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="52" t="s">
-        <v>603</v>
+        <v>664</v>
       </c>
       <c r="B70" s="52"/>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="52" t="s">
-        <v>629</v>
+        <v>675</v>
       </c>
       <c r="B71" s="52"/>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="52" t="s">
-        <v>664</v>
+        <v>678</v>
       </c>
       <c r="B72" s="52"/>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="52" t="s">
-        <v>675</v>
+        <v>633</v>
       </c>
       <c r="B73" s="52"/>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="52" t="s">
-        <v>678</v>
+        <v>614</v>
       </c>
       <c r="B74" s="52"/>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="52" t="s">
-        <v>633</v>
+        <v>663</v>
       </c>
       <c r="B75" s="52"/>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="52" t="s">
-        <v>614</v>
+        <v>679</v>
       </c>
       <c r="B76" s="52"/>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="52" t="s">
-        <v>663</v>
+        <v>639</v>
       </c>
       <c r="B77" s="52"/>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="52" t="s">
-        <v>679</v>
+        <v>640</v>
       </c>
       <c r="B78" s="52"/>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="52" t="s">
-        <v>639</v>
+        <v>604</v>
       </c>
       <c r="B79" s="52"/>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="52" t="s">
-        <v>640</v>
+        <v>676</v>
       </c>
       <c r="B80" s="52"/>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="52" t="s">
-        <v>604</v>
+        <v>659</v>
       </c>
       <c r="B81" s="52"/>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="52" t="s">
-        <v>676</v>
+        <v>660</v>
       </c>
       <c r="B82" s="52"/>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" s="52" t="s">
-        <v>659</v>
+        <v>616</v>
       </c>
       <c r="B83" s="52"/>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" s="52" t="s">
-        <v>660</v>
+        <v>636</v>
       </c>
       <c r="B84" s="52"/>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" s="52" t="s">
-        <v>616</v>
+        <v>634</v>
       </c>
       <c r="B85" s="52"/>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" s="52" t="s">
-        <v>636</v>
+        <v>605</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" s="52" t="s">
-        <v>634</v>
+        <v>729</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" s="52" t="s">
-        <v>605</v>
+        <v>652</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" s="52" t="s">
-        <v>729</v>
+        <v>674</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" s="52" t="s">
-        <v>652</v>
+        <v>626</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" s="52" t="s">
-        <v>674</v>
+        <v>606</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" s="52" t="s">
-        <v>626</v>
+        <v>599</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" s="52" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" s="52" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A95" s="52" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A96" s="52" t="s">
         <v>744</v>
       </c>
     </row>
@@ -12391,7 +12381,7 @@
       <c r="E5" s="44"/>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B6" s="71" t="s">
+      <c r="B6" s="70" t="s">
         <v>767</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -12401,7 +12391,7 @@
       <c r="E6" s="44"/>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="71"/>
+      <c r="B7" s="70"/>
       <c r="C7" s="2" t="s">
         <v>660</v>
       </c>
@@ -12409,7 +12399,7 @@
       <c r="E7" s="44"/>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="71"/>
+      <c r="B8" s="70"/>
       <c r="C8" s="2" t="s">
         <v>609</v>
       </c>
@@ -23748,14 +23738,14 @@
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A314" s="30" t="s">
-        <v>383</v>
+      <c r="A314" s="11" t="s">
+        <v>738</v>
       </c>
       <c r="B314" s="38" t="s">
-        <v>482</v>
-      </c>
-      <c r="C314" s="31">
-        <v>1</v>
+        <v>478</v>
+      </c>
+      <c r="C314" s="10">
+        <v>5.0999999999999996</v>
       </c>
       <c r="D314">
         <f t="shared" si="5"/>
@@ -23769,14 +23759,14 @@
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A315" s="30" t="s">
-        <v>383</v>
+      <c r="A315" s="11" t="s">
+        <v>738</v>
       </c>
       <c r="B315" s="38" t="s">
-        <v>481</v>
-      </c>
-      <c r="C315" s="31">
-        <v>3.1</v>
+        <v>479</v>
+      </c>
+      <c r="C315" s="10">
+        <v>3.5</v>
       </c>
       <c r="D315">
         <f t="shared" si="5"/>
@@ -23790,14 +23780,14 @@
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A316" s="30" t="s">
-        <v>383</v>
+      <c r="A316" s="11" t="s">
+        <v>738</v>
       </c>
       <c r="B316" s="38" t="s">
-        <v>479</v>
-      </c>
-      <c r="C316" s="31">
-        <v>3.5</v>
+        <v>480</v>
+      </c>
+      <c r="C316" s="10">
+        <v>2.8</v>
       </c>
       <c r="D316">
         <f t="shared" si="5"/>
@@ -23811,14 +23801,14 @@
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A317" s="30" t="s">
-        <v>383</v>
+      <c r="A317" s="11" t="s">
+        <v>738</v>
       </c>
       <c r="B317" s="38" t="s">
-        <v>478</v>
-      </c>
-      <c r="C317" s="31">
-        <v>5.0999999999999996</v>
+        <v>481</v>
+      </c>
+      <c r="C317" s="10">
+        <v>1</v>
       </c>
       <c r="D317">
         <f t="shared" si="5"/>
@@ -23832,11 +23822,11 @@
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A318" s="30" t="s">
-        <v>383</v>
+      <c r="A318" s="11" t="s">
+        <v>738</v>
       </c>
       <c r="B318" s="38" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C318" s="31">
         <v>5.4</v>
@@ -34261,7 +34251,7 @@
       <c r="A96" s="2" t="s">
         <v>744</v>
       </c>
-      <c r="B96" s="70">
+      <c r="B96" s="71">
         <v>1</v>
       </c>
     </row>
